--- a/data/nzd0020/nzd0020.xlsx
+++ b/data/nzd0020/nzd0020.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>359.28</v>
+        <v>380.46</v>
       </c>
       <c r="C252" t="n">
         <v>343.76</v>
@@ -5712,6 +5712,27 @@
       <c r="E252" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>394.58</v>
+      </c>
+      <c r="C253" t="n">
+        <v>346.89</v>
+      </c>
+      <c r="D253" t="n">
+        <v>351.74</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B259"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8319,6 +8340,16 @@
       </c>
       <c r="B259" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -8487,28 +8518,28 @@
         <v>0.0351</v>
       </c>
       <c r="I2" t="n">
-        <v>1.290949594100213</v>
+        <v>1.314995203433646</v>
       </c>
       <c r="J2" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06768102947967347</v>
+        <v>0.07081579485217804</v>
       </c>
       <c r="M2" t="n">
-        <v>28.9707940528673</v>
+        <v>28.84433159850885</v>
       </c>
       <c r="N2" t="n">
-        <v>1391.0024384096</v>
+        <v>1382.77793287546</v>
       </c>
       <c r="O2" t="n">
-        <v>37.29614508779158</v>
+        <v>37.18572216423207</v>
       </c>
       <c r="P2" t="n">
-        <v>352.0964010456557</v>
+        <v>351.8760896468272</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8565,28 +8596,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004976118668668948</v>
+        <v>-0.001901406469517155</v>
       </c>
       <c r="J3" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K3" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L3" t="n">
-        <v>2.726924907281436e-05</v>
+        <v>3.998424125573052e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>6.07479394413178</v>
+        <v>6.077710701067504</v>
       </c>
       <c r="N3" t="n">
-        <v>54.77225379875568</v>
+        <v>54.8510234731759</v>
       </c>
       <c r="O3" t="n">
-        <v>7.400827913061868</v>
+        <v>7.406147681026614</v>
       </c>
       <c r="P3" t="n">
-        <v>355.4527927881471</v>
+        <v>355.5160564354752</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8643,28 +8674,28 @@
         <v>0.078</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.118881569559372</v>
+        <v>-0.1231529293389714</v>
       </c>
       <c r="J4" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K4" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01657502526102805</v>
+        <v>0.01789516821774417</v>
       </c>
       <c r="M4" t="n">
-        <v>5.459472696395044</v>
+        <v>5.450504172060996</v>
       </c>
       <c r="N4" t="n">
-        <v>50.580168433193</v>
+        <v>50.49367173155345</v>
       </c>
       <c r="O4" t="n">
-        <v>7.111973596210338</v>
+        <v>7.105889932411946</v>
       </c>
       <c r="P4" t="n">
-        <v>360.2675995758731</v>
+        <v>360.306890133636</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8702,7 +8733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15462,7 +15493,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>-34.80418889700626,173.16580170865572</t>
+          <t>-34.80431524286721,173.1659753591106</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15478,6 +15509,33 @@
       <c r="E252" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>-34.804399473301224,173.16609112637482</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>-34.80468012345688,173.165091240795</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>-34.805358466916545,173.1646936485141</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0020/nzd0020.xlsx
+++ b/data/nzd0020/nzd0020.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>351.4</v>
+        <v>336.56</v>
       </c>
       <c r="C251" t="n">
         <v>343.96</v>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>380.46</v>
+        <v>338.98</v>
       </c>
       <c r="C252" t="n">
         <v>343.76</v>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>394.58</v>
+        <v>338.98</v>
       </c>
       <c r="C253" t="n">
         <v>346.89</v>
@@ -5731,6 +5731,48 @@
         <v>351.74</v>
       </c>
       <c r="E253" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="C254" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="D254" t="n">
+        <v>349.64</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="C255" t="n">
+        <v>345.22</v>
+      </c>
+      <c r="D255" t="n">
+        <v>349.44</v>
+      </c>
+      <c r="E255" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -5747,7 +5789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B260"/>
+  <dimension ref="A1:B262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8350,6 +8392,26 @@
       </c>
       <c r="B260" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>
@@ -8518,28 +8580,28 @@
         <v>0.0351</v>
       </c>
       <c r="I2" t="n">
-        <v>1.314995203433646</v>
+        <v>1.181831268516592</v>
       </c>
       <c r="J2" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K2" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07081579485217804</v>
+        <v>0.05795443528941535</v>
       </c>
       <c r="M2" t="n">
-        <v>28.84433159850885</v>
+        <v>28.95300685065659</v>
       </c>
       <c r="N2" t="n">
-        <v>1382.77793287546</v>
+        <v>1399.48921001693</v>
       </c>
       <c r="O2" t="n">
-        <v>37.18572216423207</v>
+        <v>37.40974752677342</v>
       </c>
       <c r="P2" t="n">
-        <v>351.8760896468272</v>
+        <v>353.0976412092731</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8596,28 +8658,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.001901406469517155</v>
+        <v>-0.01833847386146882</v>
       </c>
       <c r="J3" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K3" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L3" t="n">
-        <v>3.998424125573052e-06</v>
+        <v>0.0003730164815306525</v>
       </c>
       <c r="M3" t="n">
-        <v>6.077710701067504</v>
+        <v>6.095297481728052</v>
       </c>
       <c r="N3" t="n">
-        <v>54.8510234731759</v>
+        <v>55.28300286791566</v>
       </c>
       <c r="O3" t="n">
-        <v>7.406147681026614</v>
+        <v>7.43525405537132</v>
       </c>
       <c r="P3" t="n">
-        <v>355.5160564354752</v>
+        <v>355.6677717737147</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8674,28 +8736,28 @@
         <v>0.078</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1231529293389714</v>
+        <v>-0.1347991299088772</v>
       </c>
       <c r="J4" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K4" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01789516821774417</v>
+        <v>0.02158292436654152</v>
       </c>
       <c r="M4" t="n">
-        <v>5.450504172060996</v>
+        <v>5.443873520571565</v>
       </c>
       <c r="N4" t="n">
-        <v>50.49367173155345</v>
+        <v>50.52929129260912</v>
       </c>
       <c r="O4" t="n">
-        <v>7.105889932411946</v>
+        <v>7.10839583117099</v>
       </c>
       <c r="P4" t="n">
-        <v>360.306890133636</v>
+        <v>360.4143879555899</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8733,7 +8795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15466,7 +15528,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>-34.80414189007775,173.16573710229497</t>
+          <t>-34.80405336424461,173.16561543264712</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15493,7 +15555,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>-34.80431524286721,173.1659753591106</t>
+          <t>-34.80406780040642,173.16563527363664</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15520,7 +15582,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>-34.804399473301224,173.16609112637482</t>
+          <t>-34.80406780040642,173.16563527363664</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15534,6 +15596,60 @@
         </is>
       </c>
       <c r="E253" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>-34.80418215616714,173.16579244403349</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>-34.80466772409189,173.16506986880543</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>-34.8053493425977,173.1646735302459</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>-34.80418215616714,173.16579244403349</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>-34.80467145946585,173.16507630722842</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>-34.80534847361477,173.1646716142206</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0020/nzd0020.xlsx
+++ b/data/nzd0020/nzd0020.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>358.15</v>
+        <v>335.61</v>
       </c>
       <c r="C254" t="n">
         <v>344.5</v>
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>358.15</v>
+        <v>335.61</v>
       </c>
       <c r="C255" t="n">
         <v>345.22</v>
@@ -5775,6 +5775,27 @@
       <c r="E255" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>336.66</v>
+      </c>
+      <c r="C256" t="n">
+        <v>344.68</v>
+      </c>
+      <c r="D256" t="n">
+        <v>348.83</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B262"/>
+  <dimension ref="A1:B263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8412,6 +8433,16 @@
       </c>
       <c r="B262" t="n">
         <v>0.92</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -8580,28 +8611,28 @@
         <v>0.0351</v>
       </c>
       <c r="I2" t="n">
-        <v>1.181831268516592</v>
+        <v>1.108127719866784</v>
       </c>
       <c r="J2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K2" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05795443528941535</v>
+        <v>0.05102052909424193</v>
       </c>
       <c r="M2" t="n">
-        <v>28.95300685065659</v>
+        <v>29.05879118297799</v>
       </c>
       <c r="N2" t="n">
-        <v>1399.48921001693</v>
+        <v>1416.243784198983</v>
       </c>
       <c r="O2" t="n">
-        <v>37.40974752677342</v>
+        <v>37.63301455104258</v>
       </c>
       <c r="P2" t="n">
-        <v>353.0976412092731</v>
+        <v>353.7803740998402</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8658,28 +8689,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01833847386146882</v>
+        <v>-0.02655972249078525</v>
       </c>
       <c r="J3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003730164815306525</v>
+        <v>0.0007836871215585184</v>
       </c>
       <c r="M3" t="n">
-        <v>6.095297481728052</v>
+        <v>6.103120545240185</v>
       </c>
       <c r="N3" t="n">
-        <v>55.28300286791566</v>
+        <v>55.49284818733108</v>
       </c>
       <c r="O3" t="n">
-        <v>7.43525405537132</v>
+        <v>7.449352199173501</v>
       </c>
       <c r="P3" t="n">
-        <v>355.6677717737147</v>
+        <v>355.744655002197</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8736,28 +8767,28 @@
         <v>0.078</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1347991299088772</v>
+        <v>-0.1410552434979668</v>
       </c>
       <c r="J4" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K4" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02158292436654152</v>
+        <v>0.02369591073056587</v>
       </c>
       <c r="M4" t="n">
-        <v>5.443873520571565</v>
+        <v>5.441238918283291</v>
       </c>
       <c r="N4" t="n">
-        <v>50.52929129260912</v>
+        <v>50.57819394026306</v>
       </c>
       <c r="O4" t="n">
-        <v>7.10839583117099</v>
+        <v>7.111834780157865</v>
       </c>
       <c r="P4" t="n">
-        <v>360.4143879555899</v>
+        <v>360.472893692634</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8795,7 +8826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15609,7 +15640,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>-34.80418215616714,173.16579244403349</t>
+          <t>-34.80404769715538,173.16560764383084</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15636,7 +15667,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>-34.80418215616714,173.16579244403349</t>
+          <t>-34.80404769715538,173.16560764383084</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -15652,6 +15683,33 @@
       <c r="E255" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>-34.80405396078029,173.1656162525226</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>-34.80466865793542,173.16507147841114</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>-34.80534582321666,173.16466577034365</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0020/nzd0020.xlsx
+++ b/data/nzd0020/nzd0020.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E256"/>
+  <dimension ref="A1:E258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5796,6 +5796,48 @@
       <c r="E256" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>328.14</v>
+      </c>
+      <c r="C257" t="n">
+        <v>343.88</v>
+      </c>
+      <c r="D257" t="n">
+        <v>348.34</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>326.4</v>
+      </c>
+      <c r="C258" t="n">
+        <v>343.43</v>
+      </c>
+      <c r="D258" t="n">
+        <v>349.05</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B263"/>
+  <dimension ref="A1:B265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8443,6 +8485,26 @@
       </c>
       <c r="B263" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>-0.36</v>
       </c>
     </row>
   </sheetData>
@@ -8611,28 +8673,28 @@
         <v>0.0351</v>
       </c>
       <c r="I2" t="n">
-        <v>1.108127719866784</v>
+        <v>1.020315851777707</v>
       </c>
       <c r="J2" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K2" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05102052909424193</v>
+        <v>0.04368691879314135</v>
       </c>
       <c r="M2" t="n">
-        <v>29.05879118297799</v>
+        <v>29.09538365349352</v>
       </c>
       <c r="N2" t="n">
-        <v>1416.243784198983</v>
+        <v>1429.429440056887</v>
       </c>
       <c r="O2" t="n">
-        <v>37.63301455104258</v>
+        <v>37.807796022208</v>
       </c>
       <c r="P2" t="n">
-        <v>353.7803740998402</v>
+        <v>354.6005704548862</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8689,28 +8751,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02655972249078525</v>
+        <v>-0.04396859075717599</v>
       </c>
       <c r="J3" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K3" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007836871215585184</v>
+        <v>0.002147838489930942</v>
       </c>
       <c r="M3" t="n">
-        <v>6.103120545240185</v>
+        <v>6.124049231342494</v>
       </c>
       <c r="N3" t="n">
-        <v>55.49284818733108</v>
+        <v>56.04269753632409</v>
       </c>
       <c r="O3" t="n">
-        <v>7.449352199173501</v>
+        <v>7.486167079108246</v>
       </c>
       <c r="P3" t="n">
-        <v>355.744655002197</v>
+        <v>355.907770946994</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8767,28 +8829,28 @@
         <v>0.078</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1410552434979668</v>
+        <v>-0.1533071642633262</v>
       </c>
       <c r="J4" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K4" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02369591073056587</v>
+        <v>0.02812792226623939</v>
       </c>
       <c r="M4" t="n">
-        <v>5.441238918283291</v>
+        <v>5.438194561833124</v>
       </c>
       <c r="N4" t="n">
-        <v>50.57819394026306</v>
+        <v>50.6717274360936</v>
       </c>
       <c r="O4" t="n">
-        <v>7.111834780157865</v>
+        <v>7.118407647507524</v>
       </c>
       <c r="P4" t="n">
-        <v>360.472893692634</v>
+        <v>360.587683409008</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8826,7 +8888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E256"/>
+  <dimension ref="A1:E258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15713,6 +15775,60 @@
         </is>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>-34.8040031359204,173.1655463991755</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>-34.80466450751961,173.16506432460838</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>-34.805343694208155,173.1646610760821</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>-34.80399275619049,173.16553213336167</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>-34.804662172910525,173.16506030059463</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>-34.80534677909799,173.16466787797137</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0020/nzd0020.xlsx
+++ b/data/nzd0020/nzd0020.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E258"/>
+  <dimension ref="A1:E259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5838,6 +5838,27 @@
       <c r="E258" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>321.34</v>
+      </c>
+      <c r="C259" t="n">
+        <v>342.51</v>
+      </c>
+      <c r="D259" t="n">
+        <v>349.84</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B265"/>
+  <dimension ref="A1:B266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8505,6 +8526,16 @@
       </c>
       <c r="B265" t="n">
         <v>-0.36</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -8673,28 +8704,28 @@
         <v>0.0351</v>
       </c>
       <c r="I2" t="n">
-        <v>1.020315851777707</v>
+        <v>0.9732005418269551</v>
       </c>
       <c r="J2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04368691879314135</v>
+        <v>0.03988576771205232</v>
       </c>
       <c r="M2" t="n">
-        <v>29.09538365349352</v>
+        <v>29.1257176868397</v>
       </c>
       <c r="N2" t="n">
-        <v>1429.429440056887</v>
+        <v>1438.175154953614</v>
       </c>
       <c r="O2" t="n">
-        <v>37.807796022208</v>
+        <v>37.92327985490724</v>
       </c>
       <c r="P2" t="n">
-        <v>354.6005704548862</v>
+        <v>355.0423465997544</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8751,28 +8782,28 @@
         <v>0.09470000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04396859075717599</v>
+        <v>-0.05325812286282203</v>
       </c>
       <c r="J3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002147838489930942</v>
+        <v>0.00314577562807683</v>
       </c>
       <c r="M3" t="n">
-        <v>6.124049231342494</v>
+        <v>6.137437065750634</v>
       </c>
       <c r="N3" t="n">
-        <v>56.04269753632409</v>
+        <v>56.3968336979112</v>
       </c>
       <c r="O3" t="n">
-        <v>7.486167079108246</v>
+        <v>7.509782533330189</v>
       </c>
       <c r="P3" t="n">
-        <v>355.907770946994</v>
+        <v>355.9951446866426</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8829,28 +8860,28 @@
         <v>0.078</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1533071642633262</v>
+        <v>-0.1583520877181936</v>
       </c>
       <c r="J4" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K4" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02812792226623939</v>
+        <v>0.03013097470313675</v>
       </c>
       <c r="M4" t="n">
-        <v>5.438194561833124</v>
+        <v>5.43373824883758</v>
       </c>
       <c r="N4" t="n">
-        <v>50.6717274360936</v>
+        <v>50.64383637534875</v>
       </c>
       <c r="O4" t="n">
-        <v>7.118407647507524</v>
+        <v>7.116448297806199</v>
       </c>
       <c r="P4" t="n">
-        <v>360.587683409008</v>
+        <v>360.6351340043103</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -8888,7 +8919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E258"/>
+  <dimension ref="A1:E259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15829,6 +15860,33 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>-34.803962571449,173.16549064773935</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>-34.80465739993154,173.1650520737228</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>-34.805350211580595,173.16467544627125</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
